--- a/vignettes/data/ensemble/best_models.xlsx
+++ b/vignettes/data/ensemble/best_models.xlsx
@@ -1,21 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lsuagctr-my.sharepoint.com/personal/rtomaz_agcenter_lsu_edu/Documents/Documents/GitHub/EpiExposure/vignettes/data/ensemble/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EAAB3FD08F79A8D366075C52F37BD272EA4BDA7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F754CA85-0DAE-4EDD-BE18-59A97161EBED}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="348" yWindow="1392" windowWidth="17280" windowHeight="9036" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="35">
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>model_id</t>
+  </si>
+  <si>
+    <t>df_var</t>
+  </si>
+  <si>
+    <t>df_lag</t>
+  </si>
+  <si>
+    <t>vars</t>
+  </si>
+  <si>
+    <t>n_vars</t>
+  </si>
+  <si>
+    <t>CCC</t>
+  </si>
+  <si>
+    <t>Cb</t>
+  </si>
+  <si>
+    <t>rho</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>n_folds</t>
+  </si>
+  <si>
+    <t>n_success_folds</t>
+  </si>
+  <si>
+    <t>n_failed_folds</t>
+  </si>
+  <si>
+    <t>n_predictions</t>
+  </si>
+  <si>
+    <t>n_success</t>
+  </si>
+  <si>
+    <t>n_failed</t>
+  </si>
+  <si>
+    <t>n_warning_folds</t>
+  </si>
+  <si>
+    <t>warning_rate</t>
+  </si>
+  <si>
+    <t>n_warning_events</t>
+  </si>
+  <si>
+    <t>n_knot_warning_folds</t>
+  </si>
+  <si>
+    <t>n_convergence_warning_folds</t>
+  </si>
+  <si>
+    <t>n_hessian_warning_folds</t>
+  </si>
+  <si>
+    <t>n_other_warning_folds</t>
+  </si>
+  <si>
+    <t>n_knot_warning_events</t>
+  </si>
+  <si>
+    <t>n_convergence_warning_events</t>
+  </si>
+  <si>
+    <t>n_hessian_warning_events</t>
+  </si>
+  <si>
+    <t>n_other_warning_events</t>
+  </si>
+  <si>
+    <t>tmean + rain + wetness</t>
+  </si>
+  <si>
+    <t>tmean + wetness</t>
+  </si>
+  <si>
+    <t>rain + wetness</t>
+  </si>
+  <si>
+    <t>tmean + rain</t>
+  </si>
+  <si>
+    <t>wetness</t>
+  </si>
+  <si>
+    <t>tmean</t>
+  </si>
+  <si>
+    <t>rain</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +179,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +231,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +265,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +300,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,153 +476,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>model_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>df_var</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df_lag</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>vars</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>n_vars</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>CCC</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Cb</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>rho</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>n_folds</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>n_success_folds</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>n_failed_folds</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>n_predictions</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_success</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>n_failed</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>n_warning_folds</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>warning_rate</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>n_warning_events</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>n_knot_warning_folds</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>n_convergence_warning_folds</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>n_hessian_warning_folds</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_other_warning_folds</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>n_knot_warning_events</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_convergence_warning_events</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>n_hessian_warning_events</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>n_other_warning_events</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -509,28 +582,26 @@
       <c r="D2">
         <v>4</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>tmean + rain + wetness</t>
-        </is>
+      <c r="E2" t="s">
+        <v>28</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>0.979950158164056</v>
+        <v>0.97995015816405595</v>
       </c>
       <c r="H2">
         <v>0.9997242448267788</v>
       </c>
       <c r="I2">
-        <v>0.9802204590265299</v>
+        <v>0.98022045902652988</v>
       </c>
       <c r="J2">
-        <v>0.05291964298881337</v>
+        <v>5.2919642988813367E-2</v>
       </c>
       <c r="K2">
-        <v>0.03821928249386558</v>
+        <v>3.8219282493865581E-2</v>
       </c>
       <c r="L2">
         <v>520</v>
@@ -584,7 +655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -597,28 +668,26 @@
       <c r="D3">
         <v>4</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>tmean + rain + wetness</t>
-        </is>
+      <c r="E3" t="s">
+        <v>28</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>0.9782916129408498</v>
+        <v>0.97829161294084976</v>
       </c>
       <c r="H3">
-        <v>0.9996410900831298</v>
+        <v>0.99964109008312985</v>
       </c>
       <c r="I3">
         <v>0.9786428575675048</v>
       </c>
       <c r="J3">
-        <v>0.05497623947223665</v>
+        <v>5.4976239472236649E-2</v>
       </c>
       <c r="K3">
-        <v>0.03951957186975079</v>
+        <v>3.9519571869750789E-2</v>
       </c>
       <c r="L3">
         <v>520</v>
@@ -672,7 +741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -685,28 +754,26 @@
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>tmean + rain + wetness</t>
-        </is>
+      <c r="E4" t="s">
+        <v>28</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>0.9701868525892332</v>
+        <v>0.97018685258923321</v>
       </c>
       <c r="H4">
-        <v>0.9993807576911117</v>
+        <v>0.99938075769111168</v>
       </c>
       <c r="I4">
-        <v>0.9707880055952591</v>
+        <v>0.97078800559525913</v>
       </c>
       <c r="J4">
-        <v>0.06416849493374555</v>
+        <v>6.4168494933745546E-2</v>
       </c>
       <c r="K4">
-        <v>0.04748532025333416</v>
+        <v>4.7485320253334157E-2</v>
       </c>
       <c r="L4">
         <v>520</v>
@@ -760,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -773,28 +840,26 @@
       <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>tmean + rain + wetness</t>
-        </is>
+      <c r="E5" t="s">
+        <v>28</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5">
-        <v>0.9687742178427846</v>
+        <v>0.96877421784278461</v>
       </c>
       <c r="H5">
-        <v>0.99926394184089</v>
+        <v>0.99926394184088996</v>
       </c>
       <c r="I5">
-        <v>0.9694878172608372</v>
+        <v>0.96948781726083721</v>
       </c>
       <c r="J5">
-        <v>0.06557171504657712</v>
+        <v>6.557171504657712E-2</v>
       </c>
       <c r="K5">
-        <v>0.04834563651066225</v>
+        <v>4.8345636510662253E-2</v>
       </c>
       <c r="L5">
         <v>520</v>
@@ -848,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -861,28 +926,26 @@
       <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>tmean + rain + wetness</t>
-        </is>
+      <c r="E6" t="s">
+        <v>28</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6">
-        <v>0.952265797576562</v>
+        <v>0.95226579757656205</v>
       </c>
       <c r="H6">
-        <v>0.9982316178154013</v>
+        <v>0.99823161781540126</v>
       </c>
       <c r="I6">
         <v>0.9539527506257176</v>
       </c>
       <c r="J6">
-        <v>0.08027343312751634</v>
+        <v>8.0273433127516336E-2</v>
       </c>
       <c r="K6">
-        <v>0.05770645164938885</v>
+        <v>5.7706451649388847E-2</v>
       </c>
       <c r="L6">
         <v>520</v>
@@ -936,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -949,28 +1012,26 @@
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>tmean + rain + wetness</t>
-        </is>
+      <c r="E7" t="s">
+        <v>28</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
-        <v>0.9492879323778345</v>
+        <v>0.94928793237783449</v>
       </c>
       <c r="H7">
-        <v>0.9978858149749</v>
+        <v>0.99788581497490003</v>
       </c>
       <c r="I7">
-        <v>0.9512991548053141</v>
+        <v>0.95129915480531413</v>
       </c>
       <c r="J7">
-        <v>0.08253415430104309</v>
+        <v>8.2534154301043092E-2</v>
       </c>
       <c r="K7">
-        <v>0.05886408240683829</v>
+        <v>5.886408240683829E-2</v>
       </c>
       <c r="L7">
         <v>520</v>
@@ -1024,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1037,10 +1098,8 @@
       <c r="D8">
         <v>4</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E8" t="s">
+        <v>29</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -1049,16 +1108,16 @@
         <v>0.8590462606372582</v>
       </c>
       <c r="H8">
-        <v>0.9863055968283946</v>
+        <v>0.98630559682839458</v>
       </c>
       <c r="I8">
-        <v>0.8709737259928801</v>
+        <v>0.87097372599288014</v>
       </c>
       <c r="J8">
-        <v>0.1315838789232578</v>
+        <v>0.13158387892325779</v>
       </c>
       <c r="K8">
-        <v>0.09884824537399875</v>
+        <v>9.884824537399875E-2</v>
       </c>
       <c r="L8">
         <v>520</v>
@@ -1112,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1125,10 +1184,8 @@
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E9" t="s">
+        <v>29</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1140,13 +1197,13 @@
         <v>0.9868657835467578</v>
       </c>
       <c r="I9">
-        <v>0.8689210376357245</v>
+        <v>0.86892103763572448</v>
       </c>
       <c r="J9">
-        <v>0.1324930450251554</v>
+        <v>0.13249304502515541</v>
       </c>
       <c r="K9">
-        <v>0.09975795303260186</v>
+        <v>9.9757953032601862E-2</v>
       </c>
       <c r="L9">
         <v>520</v>
@@ -1200,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1213,28 +1270,26 @@
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E10" t="s">
+        <v>29</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10">
-        <v>0.8511271205223407</v>
+        <v>0.85112712052234074</v>
       </c>
       <c r="H10">
-        <v>0.9834195341555106</v>
+        <v>0.98341953415551064</v>
       </c>
       <c r="I10">
-        <v>0.8654771345916237</v>
+        <v>0.86547713459162368</v>
       </c>
       <c r="J10">
-        <v>0.1343171871121235</v>
+        <v>0.13431718711212351</v>
       </c>
       <c r="K10">
-        <v>0.1016222163948445</v>
+        <v>0.10162221639484451</v>
       </c>
       <c r="L10">
         <v>520</v>
@@ -1288,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1301,22 +1356,20 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E11" t="s">
+        <v>29</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>0.8482492764943894</v>
+        <v>0.84824927649438941</v>
       </c>
       <c r="H11">
-        <v>0.983678436853294</v>
+        <v>0.98367843685329404</v>
       </c>
       <c r="I11">
-        <v>0.8623237480002802</v>
+        <v>0.86232374800028022</v>
       </c>
       <c r="J11">
         <v>0.1356710618849967</v>
@@ -1376,7 +1429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1389,22 +1442,20 @@
       <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E12" t="s">
+        <v>29</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12">
-        <v>0.8478974969470973</v>
+        <v>0.84789749694709726</v>
       </c>
       <c r="H12">
-        <v>0.9835756828773879</v>
+        <v>0.98357568287738795</v>
       </c>
       <c r="I12">
-        <v>0.8620561810420396</v>
+        <v>0.86205618104203963</v>
       </c>
       <c r="J12">
         <v>0.1357881844755813</v>
@@ -1464,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1477,28 +1528,26 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E13" t="s">
+        <v>29</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>0.8459621148264678</v>
+        <v>0.84596211482646777</v>
       </c>
       <c r="H13">
-        <v>0.9839654237723715</v>
+        <v>0.98396542377237151</v>
       </c>
       <c r="I13">
-        <v>0.8597478065674093</v>
+        <v>0.85974780656740935</v>
       </c>
       <c r="J13">
-        <v>0.1367661341187663</v>
+        <v>0.13676613411876631</v>
       </c>
       <c r="K13">
-        <v>0.10394391831851</v>
+        <v>0.10394391831851001</v>
       </c>
       <c r="L13">
         <v>520</v>
@@ -1552,7 +1601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1565,10 +1614,8 @@
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E14" t="s">
+        <v>29</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1577,13 +1624,13 @@
         <v>0.8454527605956127</v>
       </c>
       <c r="H14">
-        <v>0.9826344802823939</v>
+        <v>0.98263448028239386</v>
       </c>
       <c r="I14">
-        <v>0.8603939486762593</v>
+        <v>0.86039394867625929</v>
       </c>
       <c r="J14">
-        <v>0.1366126289942295</v>
+        <v>0.13661262899422949</v>
       </c>
       <c r="K14">
         <v>0.1040393441825625</v>
@@ -1640,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1653,28 +1700,26 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E15" t="s">
+        <v>29</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15">
-        <v>0.8388638825128004</v>
+        <v>0.83886388251280042</v>
       </c>
       <c r="H15">
         <v>0.9802705699327201</v>
       </c>
       <c r="I15">
-        <v>0.8557472888024936</v>
+        <v>0.85574728880249362</v>
       </c>
       <c r="J15">
-        <v>0.1387880382455587</v>
+        <v>0.13878803824555869</v>
       </c>
       <c r="K15">
-        <v>0.1060570396347806</v>
+        <v>0.10605703963478059</v>
       </c>
       <c r="L15">
         <v>520</v>
@@ -1728,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1741,25 +1786,23 @@
       <c r="D16">
         <v>2</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>tmean + wetness</t>
-        </is>
+      <c r="E16" t="s">
+        <v>29</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16">
-        <v>0.8371256120037543</v>
+        <v>0.83712561200375435</v>
       </c>
       <c r="H16">
-        <v>0.9796058325993285</v>
+        <v>0.97960583259932854</v>
       </c>
       <c r="I16">
-        <v>0.854553519533963</v>
+        <v>0.85455351953396297</v>
       </c>
       <c r="J16">
-        <v>0.1393632266132772</v>
+        <v>0.13936322661327721</v>
       </c>
       <c r="K16">
         <v>0.1068670817970068</v>
@@ -1816,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1829,22 +1872,20 @@
       <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>rain + wetness</t>
-        </is>
+      <c r="E17" t="s">
+        <v>30</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17">
-        <v>0.7196489319286843</v>
+        <v>0.71964893192868429</v>
       </c>
       <c r="H17">
-        <v>0.9542740669384183</v>
+        <v>0.95427406693841832</v>
       </c>
       <c r="I17">
-        <v>0.7541323366750624</v>
+        <v>0.75413233667506241</v>
       </c>
       <c r="J17">
         <v>0.1757318402802894</v>
@@ -1904,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1917,28 +1958,26 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>rain + wetness</t>
-        </is>
+      <c r="E18" t="s">
+        <v>30</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18">
-        <v>0.7176222357716626</v>
+        <v>0.71762223577166262</v>
       </c>
       <c r="H18">
-        <v>0.9496123408961368</v>
+        <v>0.94961234089613678</v>
       </c>
       <c r="I18">
-        <v>0.7557001998251748</v>
+        <v>0.75570019982517478</v>
       </c>
       <c r="J18">
-        <v>0.1754329357241046</v>
+        <v>0.17543293572410459</v>
       </c>
       <c r="K18">
-        <v>0.1438593485144914</v>
+        <v>0.14385934851449139</v>
       </c>
       <c r="L18">
         <v>520</v>
@@ -1992,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2005,28 +2044,26 @@
       <c r="D19">
         <v>4</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>rain + wetness</t>
-        </is>
+      <c r="E19" t="s">
+        <v>30</v>
       </c>
       <c r="F19">
         <v>2</v>
       </c>
       <c r="G19">
-        <v>0.7169632040812435</v>
+        <v>0.71696320408124348</v>
       </c>
       <c r="H19">
-        <v>0.9508183834055576</v>
+        <v>0.95081838340555758</v>
       </c>
       <c r="I19">
         <v>0.7540485297657874</v>
       </c>
       <c r="J19">
-        <v>0.1758844605202242</v>
+        <v>0.17588446052022419</v>
       </c>
       <c r="K19">
-        <v>0.1447545109610072</v>
+        <v>0.14475451096100719</v>
       </c>
       <c r="L19">
         <v>520</v>
@@ -2080,7 +2117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2093,25 +2130,23 @@
       <c r="D20">
         <v>3</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>rain + wetness</t>
-        </is>
+      <c r="E20" t="s">
+        <v>30</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20">
-        <v>0.7149541024912957</v>
+        <v>0.71495410249129565</v>
       </c>
       <c r="H20">
-        <v>0.9508146141299095</v>
+        <v>0.95081461412990953</v>
       </c>
       <c r="I20">
-        <v>0.7519384871314269</v>
+        <v>0.75193848713142686</v>
       </c>
       <c r="J20">
-        <v>0.1764792327069223</v>
+        <v>0.17647923270692231</v>
       </c>
       <c r="K20">
         <v>0.1447793963896343</v>
@@ -2168,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2181,25 +2216,23 @@
       <c r="D21">
         <v>2</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>rain + wetness</t>
-        </is>
+      <c r="E21" t="s">
+        <v>30</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>0.6905869946397264</v>
+        <v>0.69058699463972639</v>
       </c>
       <c r="H21">
-        <v>0.9403376293092823</v>
+        <v>0.94033762930928233</v>
       </c>
       <c r="I21">
         <v>0.7344032325357347</v>
       </c>
       <c r="J21">
-        <v>0.1818319963347226</v>
+        <v>0.18183199633472261</v>
       </c>
       <c r="K21">
         <v>0.1491406552702936</v>
@@ -2256,7 +2289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2269,16 +2302,14 @@
       <c r="D22">
         <v>2</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>rain + wetness</t>
-        </is>
+      <c r="E22" t="s">
+        <v>30</v>
       </c>
       <c r="F22">
         <v>2</v>
       </c>
       <c r="G22">
-        <v>0.6889625452670983</v>
+        <v>0.68896254526709833</v>
       </c>
       <c r="H22">
         <v>0.9415267617744667</v>
@@ -2287,10 +2318,10 @@
         <v>0.7317503582889473</v>
       </c>
       <c r="J22">
-        <v>0.182525470654444</v>
+        <v>0.18252547065444399</v>
       </c>
       <c r="K22">
-        <v>0.1500072307487501</v>
+        <v>0.15000723074875011</v>
       </c>
       <c r="L22">
         <v>520</v>
@@ -2344,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2357,10 +2388,8 @@
       <c r="D23">
         <v>4</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>tmean + rain</t>
-        </is>
+      <c r="E23" t="s">
+        <v>31</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -2369,13 +2398,13 @@
         <v>0.66719757022741</v>
       </c>
       <c r="H23">
-        <v>0.9400284583990497</v>
+        <v>0.94002845839904969</v>
       </c>
       <c r="I23">
-        <v>0.7097631611746155</v>
+        <v>0.70976316117461546</v>
       </c>
       <c r="J23">
-        <v>0.1886227781733275</v>
+        <v>0.18862277817332751</v>
       </c>
       <c r="K23">
         <v>0.1558668430052432</v>
@@ -2432,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2445,22 +2474,20 @@
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>tmean + rain</t>
-        </is>
+      <c r="E24" t="s">
+        <v>31</v>
       </c>
       <c r="F24">
         <v>2</v>
       </c>
       <c r="G24">
-        <v>0.6528311341156038</v>
+        <v>0.65283113411560378</v>
       </c>
       <c r="H24">
-        <v>0.931213229881152</v>
+        <v>0.93121322988115196</v>
       </c>
       <c r="I24">
-        <v>0.7010544021146721</v>
+        <v>0.70105440211467207</v>
       </c>
       <c r="J24">
         <v>0.1909923820573538</v>
@@ -2520,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2533,28 +2560,26 @@
       <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>tmean + rain</t>
-        </is>
+      <c r="E25" t="s">
+        <v>31</v>
       </c>
       <c r="F25">
         <v>2</v>
       </c>
       <c r="G25">
-        <v>0.6512330446620629</v>
+        <v>0.65123304466206289</v>
       </c>
       <c r="H25">
-        <v>0.9318652071301703</v>
+        <v>0.93186520713017029</v>
       </c>
       <c r="I25">
-        <v>0.6988489748078914</v>
+        <v>0.69884897480789143</v>
       </c>
       <c r="J25">
-        <v>0.1915432604149389</v>
+        <v>0.19154326041493891</v>
       </c>
       <c r="K25">
-        <v>0.158639908657921</v>
+        <v>0.15863990865792099</v>
       </c>
       <c r="L25">
         <v>520</v>
@@ -2608,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2621,28 +2646,26 @@
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>tmean + rain</t>
-        </is>
+      <c r="E26" t="s">
+        <v>31</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26">
-        <v>0.6442604886177106</v>
+        <v>0.64426048861771057</v>
       </c>
       <c r="H26">
-        <v>0.9259098932808812</v>
+        <v>0.92590989328088125</v>
       </c>
       <c r="I26">
-        <v>0.6958133758943102</v>
+        <v>0.69581337589431025</v>
       </c>
       <c r="J26">
-        <v>0.1924196140133874</v>
+        <v>0.19241961401338739</v>
       </c>
       <c r="K26">
-        <v>0.1597804180465117</v>
+        <v>0.15978041804651169</v>
       </c>
       <c r="L26">
         <v>520</v>
@@ -2696,7 +2719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2709,28 +2732,26 @@
       <c r="D27">
         <v>2</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>tmean + rain</t>
-        </is>
+      <c r="E27" t="s">
+        <v>31</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27">
-        <v>0.6359820427152513</v>
+        <v>0.63598204271525127</v>
       </c>
       <c r="H27">
-        <v>0.9197229257017338</v>
+        <v>0.91972292570173375</v>
       </c>
       <c r="I27">
-        <v>0.6914930844308435</v>
+        <v>0.69149308443084345</v>
       </c>
       <c r="J27">
-        <v>0.1935887711224843</v>
+        <v>0.19358877112248429</v>
       </c>
       <c r="K27">
-        <v>0.1606782285375603</v>
+        <v>0.16067822853756031</v>
       </c>
       <c r="L27">
         <v>520</v>
@@ -2784,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2797,28 +2818,26 @@
       <c r="D28">
         <v>2</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>tmean + rain</t>
-        </is>
+      <c r="E28" t="s">
+        <v>31</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28">
-        <v>0.6305787285007819</v>
+        <v>0.63057872850078189</v>
       </c>
       <c r="H28">
-        <v>0.9155385914288812</v>
+        <v>0.91553859142888117</v>
       </c>
       <c r="I28">
-        <v>0.6887516642161829</v>
+        <v>0.68875166421618295</v>
       </c>
       <c r="J28">
-        <v>0.1943716299172568</v>
+        <v>0.19437162991725679</v>
       </c>
       <c r="K28">
-        <v>0.1604889982098709</v>
+        <v>0.16048899820987089</v>
       </c>
       <c r="L28">
         <v>520</v>
@@ -2872,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2885,25 +2904,23 @@
       <c r="D29">
         <v>2</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E29" t="s">
+        <v>32</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29">
-        <v>0.5467469030659569</v>
+        <v>0.54674690306595686</v>
       </c>
       <c r="H29">
-        <v>0.8854260323006857</v>
+        <v>0.88542603230068573</v>
       </c>
       <c r="I29">
-        <v>0.6174958529797153</v>
+        <v>0.61749585297971532</v>
       </c>
       <c r="J29">
-        <v>0.2105034997380345</v>
+        <v>0.21050349973803451</v>
       </c>
       <c r="K29">
         <v>0.176043242531912</v>
@@ -2960,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2973,28 +2990,26 @@
       <c r="D30">
         <v>2</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E30" t="s">
+        <v>32</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30">
-        <v>0.5463497234813487</v>
+        <v>0.54634972348134869</v>
       </c>
       <c r="H30">
-        <v>0.8818085321975173</v>
+        <v>0.88180853219751731</v>
       </c>
       <c r="I30">
-        <v>0.6195786313382723</v>
+        <v>0.61957863133827229</v>
       </c>
       <c r="J30">
         <v>0.210118622666713</v>
       </c>
       <c r="K30">
-        <v>0.1763155991294449</v>
+        <v>0.17631559912944489</v>
       </c>
       <c r="L30">
         <v>520</v>
@@ -3048,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3061,28 +3076,26 @@
       <c r="D31">
         <v>4</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E31" t="s">
+        <v>32</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
-        <v>0.5441859314192204</v>
+        <v>0.54418593141922045</v>
       </c>
       <c r="H31">
-        <v>0.8880555948947013</v>
+        <v>0.88805559489470132</v>
       </c>
       <c r="I31">
-        <v>0.6127836303804219</v>
+        <v>0.61278363038042194</v>
       </c>
       <c r="J31">
-        <v>0.2114399943011605</v>
+        <v>0.21143999430116051</v>
       </c>
       <c r="K31">
-        <v>0.1763837361263313</v>
+        <v>0.17638373612633129</v>
       </c>
       <c r="L31">
         <v>520</v>
@@ -3136,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3149,22 +3162,20 @@
       <c r="D32">
         <v>4</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E32" t="s">
+        <v>32</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>0.5440905267547507</v>
+        <v>0.54409052675475067</v>
       </c>
       <c r="H32">
-        <v>0.8840029036717422</v>
+        <v>0.88400290367174217</v>
       </c>
       <c r="I32">
-        <v>0.6154849995343323</v>
+        <v>0.61548499953433233</v>
       </c>
       <c r="J32">
         <v>0.2109359457670249</v>
@@ -3224,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3237,28 +3248,26 @@
       <c r="D33">
         <v>3</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E33" t="s">
+        <v>32</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>0.5427495331834251</v>
+        <v>0.54274953318342511</v>
       </c>
       <c r="H33">
-        <v>0.8820439836111251</v>
+        <v>0.88204398361112513</v>
       </c>
       <c r="I33">
-        <v>0.6153315971402988</v>
+        <v>0.61533159714029884</v>
       </c>
       <c r="J33">
-        <v>0.2109711399074354</v>
+        <v>0.21097113990743541</v>
       </c>
       <c r="K33">
-        <v>0.1767370510046737</v>
+        <v>0.17673705100467371</v>
       </c>
       <c r="L33">
         <v>520</v>
@@ -3312,7 +3321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3325,28 +3334,26 @@
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E34" t="s">
+        <v>32</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>0.5426556683909164</v>
+        <v>0.54265566839091639</v>
       </c>
       <c r="H34">
-        <v>0.8856290564954943</v>
+        <v>0.88562905649549428</v>
       </c>
       <c r="I34">
-        <v>0.612734715974935</v>
+        <v>0.61273471597493501</v>
       </c>
       <c r="J34">
         <v>0.2114562134554161</v>
       </c>
       <c r="K34">
-        <v>0.1766585900415455</v>
+        <v>0.17665859004154549</v>
       </c>
       <c r="L34">
         <v>520</v>
@@ -3400,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3413,28 +3420,26 @@
       <c r="D35">
         <v>4</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E35" t="s">
+        <v>33</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35">
-        <v>0.5399201475986962</v>
+        <v>0.53992014759869622</v>
       </c>
       <c r="H35">
-        <v>0.8742315837508298</v>
+        <v>0.87423158375082977</v>
       </c>
       <c r="I35">
-        <v>0.6175939620966407</v>
+        <v>0.61759396209664075</v>
       </c>
       <c r="J35">
         <v>0.2107151639103583</v>
       </c>
       <c r="K35">
-        <v>0.1703005248956544</v>
+        <v>0.17030052489565439</v>
       </c>
       <c r="L35">
         <v>520</v>
@@ -3488,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3501,28 +3506,26 @@
       <c r="D36">
         <v>2</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E36" t="s">
+        <v>32</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>0.5379799465380435</v>
+        <v>0.53797994653804349</v>
       </c>
       <c r="H36">
-        <v>0.8739832430430249</v>
+        <v>0.87398324304302488</v>
       </c>
       <c r="I36">
-        <v>0.6155494980257413</v>
+        <v>0.61554949802574133</v>
       </c>
       <c r="J36">
-        <v>0.2109983148860265</v>
+        <v>0.21099831488602649</v>
       </c>
       <c r="K36">
-        <v>0.1773782629401529</v>
+        <v>0.17737826294015291</v>
       </c>
       <c r="L36">
         <v>520</v>
@@ -3576,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3589,28 +3592,26 @@
       <c r="D37">
         <v>4</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E37" t="s">
+        <v>32</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37">
-        <v>0.5361057779822851</v>
+        <v>0.53610577798228509</v>
       </c>
       <c r="H37">
-        <v>0.8769194866110689</v>
+        <v>0.87691948661106889</v>
       </c>
       <c r="I37">
-        <v>0.6113511971938407</v>
+        <v>0.61135119719384068</v>
       </c>
       <c r="J37">
-        <v>0.2118140747253059</v>
+        <v>0.21181407472530589</v>
       </c>
       <c r="K37">
-        <v>0.1780267780205964</v>
+        <v>0.17802677802059641</v>
       </c>
       <c r="L37">
         <v>520</v>
@@ -3664,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3677,28 +3678,26 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>wetness</t>
-        </is>
+      <c r="E38" t="s">
+        <v>32</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38">
-        <v>0.5355164395611555</v>
+        <v>0.53551643956115547</v>
       </c>
       <c r="H38">
-        <v>0.8745285643233532</v>
+        <v>0.87452856432335324</v>
       </c>
       <c r="I38">
         <v>0.6123487115317946</v>
       </c>
       <c r="J38">
-        <v>0.2116276730925293</v>
+        <v>0.21162767309252931</v>
       </c>
       <c r="K38">
-        <v>0.1777475484830716</v>
+        <v>0.17774754848307159</v>
       </c>
       <c r="L38">
         <v>520</v>
@@ -3752,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3765,28 +3764,26 @@
       <c r="D39">
         <v>4</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E39" t="s">
+        <v>33</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39">
-        <v>0.5321542318159114</v>
+        <v>0.53215423181591137</v>
       </c>
       <c r="H39">
-        <v>0.868132336306994</v>
+        <v>0.86813233630699405</v>
       </c>
       <c r="I39">
-        <v>0.6129874554375866</v>
+        <v>0.61298745543758659</v>
       </c>
       <c r="J39">
-        <v>0.2116883144437491</v>
+        <v>0.21168831444374911</v>
       </c>
       <c r="K39">
-        <v>0.1726965976502161</v>
+        <v>0.17269659765021611</v>
       </c>
       <c r="L39">
         <v>520</v>
@@ -3840,7 +3837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3853,28 +3850,26 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E40" t="s">
+        <v>33</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40">
-        <v>0.5209950066213321</v>
+        <v>0.52099500662133214</v>
       </c>
       <c r="H40">
-        <v>0.859283706934251</v>
+        <v>0.85928370693425105</v>
       </c>
       <c r="I40">
-        <v>0.6063131447937447</v>
+        <v>0.60631314479374465</v>
       </c>
       <c r="J40">
         <v>0.2131309793803407</v>
       </c>
       <c r="K40">
-        <v>0.1744216535916633</v>
+        <v>0.17442165359166331</v>
       </c>
       <c r="L40">
         <v>520</v>
@@ -3928,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3941,28 +3936,26 @@
       <c r="D41">
         <v>2</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E41" t="s">
+        <v>33</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>0.5209795549793105</v>
+        <v>0.52097955497931048</v>
       </c>
       <c r="H41">
-        <v>0.8538269047907326</v>
+        <v>0.85382690479073264</v>
       </c>
       <c r="I41">
-        <v>0.6101699911962826</v>
+        <v>0.61016999119628257</v>
       </c>
       <c r="J41">
-        <v>0.2125153159667935</v>
+        <v>0.21251531596679349</v>
       </c>
       <c r="K41">
-        <v>0.1743988361503191</v>
+        <v>0.17439883615031909</v>
       </c>
       <c r="L41">
         <v>520</v>
@@ -4016,7 +4009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4029,25 +4022,23 @@
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E42" t="s">
+        <v>33</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42">
-        <v>0.5183539453322357</v>
+        <v>0.51835394533223567</v>
       </c>
       <c r="H42">
-        <v>0.8557573039919494</v>
+        <v>0.85575730399194938</v>
       </c>
       <c r="I42">
-        <v>0.6057254117659417</v>
+        <v>0.60572541176594175</v>
       </c>
       <c r="J42">
-        <v>0.2133057858685098</v>
+        <v>0.21330578586850979</v>
       </c>
       <c r="K42">
         <v>0.1747233108792331</v>
@@ -4104,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4117,25 +4108,23 @@
       <c r="D43">
         <v>4</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E43" t="s">
+        <v>33</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>0.518301381810877</v>
+        <v>0.51830138181087704</v>
       </c>
       <c r="H43">
-        <v>0.8504884738594566</v>
+        <v>0.85048847385945658</v>
       </c>
       <c r="I43">
-        <v>0.6094161152576966</v>
+        <v>0.60941611525769657</v>
       </c>
       <c r="J43">
-        <v>0.2127358550780482</v>
+        <v>0.21273585507804821</v>
       </c>
       <c r="K43">
         <v>0.1737325156485765</v>
@@ -4192,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4205,28 +4194,26 @@
       <c r="D44">
         <v>2</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E44" t="s">
+        <v>33</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>0.5144393273657739</v>
+        <v>0.51443932736577391</v>
       </c>
       <c r="H44">
-        <v>0.8495674015710699</v>
+        <v>0.84956740157106991</v>
       </c>
       <c r="I44">
-        <v>0.6055309165752387</v>
+        <v>0.60553091657523872</v>
       </c>
       <c r="J44">
         <v>0.2134890528083476</v>
       </c>
       <c r="K44">
-        <v>0.1747109288186036</v>
+        <v>0.17471092881860359</v>
       </c>
       <c r="L44">
         <v>520</v>
@@ -4280,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4293,28 +4280,26 @@
       <c r="D45">
         <v>2</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E45" t="s">
+        <v>33</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45">
-        <v>0.5061850333805495</v>
+        <v>0.50618503338054954</v>
       </c>
       <c r="H45">
-        <v>0.8409302288768649</v>
+        <v>0.84093022887686486</v>
       </c>
       <c r="I45">
-        <v>0.6019346385687711</v>
+        <v>0.60193463856877105</v>
       </c>
       <c r="J45">
-        <v>0.2143493823029038</v>
+        <v>0.21434938230290379</v>
       </c>
       <c r="K45">
-        <v>0.1755940309333112</v>
+        <v>0.17559403093331119</v>
       </c>
       <c r="L45">
         <v>520</v>
@@ -4368,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4381,28 +4366,26 @@
       <c r="D46">
         <v>3</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>tmean</t>
-        </is>
+      <c r="E46" t="s">
+        <v>33</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46">
-        <v>0.5035189333500776</v>
+        <v>0.50351893335007758</v>
       </c>
       <c r="H46">
-        <v>0.8408276415852496</v>
+        <v>0.84082764158524959</v>
       </c>
       <c r="I46">
-        <v>0.5988372746651989</v>
+        <v>0.59883727466519887</v>
       </c>
       <c r="J46">
-        <v>0.2149083244898765</v>
+        <v>0.21490832448987651</v>
       </c>
       <c r="K46">
-        <v>0.1758913893121578</v>
+        <v>0.17589138931215781</v>
       </c>
       <c r="L46">
         <v>520</v>
@@ -4456,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4469,28 +4452,26 @@
       <c r="D47">
         <v>4</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
+      <c r="E47" t="s">
+        <v>34</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47">
-        <v>0.2450375005707693</v>
+        <v>0.24503750057076931</v>
       </c>
       <c r="H47">
-        <v>0.6688355921618208</v>
+        <v>0.66883559216182076</v>
       </c>
       <c r="I47">
-        <v>0.3663643254671231</v>
+        <v>0.36636432546712311</v>
       </c>
       <c r="J47">
         <v>0.2489908502028701</v>
       </c>
       <c r="K47">
-        <v>0.2102703751875215</v>
+        <v>0.21027037518752151</v>
       </c>
       <c r="L47">
         <v>520</v>
@@ -4544,7 +4525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4557,28 +4538,26 @@
       <c r="D48">
         <v>3</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
+      <c r="E48" t="s">
+        <v>34</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48">
-        <v>0.2255553133808242</v>
+        <v>0.22555531338082421</v>
       </c>
       <c r="H48">
         <v>0.6399227559241164</v>
       </c>
       <c r="I48">
-        <v>0.3524727184534927</v>
+        <v>0.35247271845349271</v>
       </c>
       <c r="J48">
-        <v>0.2504022687552602</v>
+        <v>0.25040226875526023</v>
       </c>
       <c r="K48">
-        <v>0.2117280848195053</v>
+        <v>0.21172808481950531</v>
       </c>
       <c r="L48">
         <v>520</v>
@@ -4632,7 +4611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4645,28 +4624,26 @@
       <c r="D49">
         <v>4</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
+      <c r="E49" t="s">
+        <v>34</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49">
-        <v>0.2236187384142684</v>
+        <v>0.22361873841426841</v>
       </c>
       <c r="H49">
         <v>0.6415229813670561</v>
       </c>
       <c r="I49">
-        <v>0.3485747898504697</v>
+        <v>0.34857478985046969</v>
       </c>
       <c r="J49">
-        <v>0.2508076597938882</v>
+        <v>0.25080765979388819</v>
       </c>
       <c r="K49">
-        <v>0.2134910888331928</v>
+        <v>0.21349108883319279</v>
       </c>
       <c r="L49">
         <v>520</v>
@@ -4720,7 +4697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4733,10 +4710,8 @@
       <c r="D50">
         <v>3</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
+      <c r="E50" t="s">
+        <v>34</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -4745,16 +4720,16 @@
         <v>0.2194981032778619</v>
       </c>
       <c r="H50">
-        <v>0.627355850605463</v>
+        <v>0.62735585060546295</v>
       </c>
       <c r="I50">
-        <v>0.3498781482089051</v>
+        <v>0.34987814820890512</v>
       </c>
       <c r="J50">
-        <v>0.2506561708889831</v>
+        <v>0.25065617088898312</v>
       </c>
       <c r="K50">
-        <v>0.2125269845923898</v>
+        <v>0.21252698459238981</v>
       </c>
       <c r="L50">
         <v>520</v>
@@ -4808,7 +4783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4821,28 +4796,26 @@
       <c r="D51">
         <v>2</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
+      <c r="E51" t="s">
+        <v>34</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51">
-        <v>0.1839686743308448</v>
+        <v>0.18396867433084479</v>
       </c>
       <c r="H51">
-        <v>0.5766624021692247</v>
+        <v>0.57666240216922471</v>
       </c>
       <c r="I51">
-        <v>0.319023181741712</v>
+        <v>0.31902318174171201</v>
       </c>
       <c r="J51">
-        <v>0.2535699444090383</v>
+        <v>0.25356994440903829</v>
       </c>
       <c r="K51">
-        <v>0.2164707662196197</v>
+        <v>0.21647076621961969</v>
       </c>
       <c r="L51">
         <v>520</v>
@@ -4896,7 +4869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4909,25 +4882,23 @@
       <c r="D52">
         <v>2</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
+      <c r="E52" t="s">
+        <v>34</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52">
-        <v>0.1794750237467796</v>
+        <v>0.17947502374677959</v>
       </c>
       <c r="H52">
-        <v>0.5783540972605692</v>
+        <v>0.57835409726056919</v>
       </c>
       <c r="I52">
-        <v>0.3103203117205888</v>
+        <v>0.31032031172058883</v>
       </c>
       <c r="J52">
-        <v>0.2543511485182869</v>
+        <v>0.25435114851828688</v>
       </c>
       <c r="K52">
         <v>0.2170930003766372</v>
